--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0001T0006Z000C1N56_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0001T0006Z000C1N56_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>30.21847357285436</v>
+        <v>4.910501955588833</v>
       </c>
       <c r="D2" t="n">
-        <v>41.50401323824954</v>
+        <v>6.74440215121555</v>
       </c>
       <c r="E2" t="n">
-        <v>3.683420782222806</v>
+        <v>0.5985558771112059</v>
       </c>
       <c r="F2" t="n">
-        <v>7.869564338494824</v>
+        <v>1.278804205005409</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.87662771517969</v>
+        <v>4.042452003716699</v>
       </c>
       <c r="D3" t="n">
-        <v>23.17021405581216</v>
+        <v>3.765159784069477</v>
       </c>
       <c r="E3" t="n">
-        <v>3.683420782222806</v>
+        <v>0.5985558771112059</v>
       </c>
       <c r="F3" t="n">
-        <v>7.869564338494824</v>
+        <v>1.278804205005409</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>21.33138346648995</v>
+        <v>3.466349813304617</v>
       </c>
       <c r="D4" t="n">
-        <v>22.20010061015462</v>
+        <v>3.607516349150127</v>
       </c>
       <c r="E4" t="n">
-        <v>3.683420782222806</v>
+        <v>0.5985558771112059</v>
       </c>
       <c r="F4" t="n">
-        <v>7.869564338494824</v>
+        <v>1.278804205005409</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>29.83320172582612</v>
+        <v>4.847895280446744</v>
       </c>
       <c r="D5" t="n">
-        <v>25.10236846064436</v>
+        <v>4.079134874854708</v>
       </c>
       <c r="E5" t="n">
-        <v>3.683420782222806</v>
+        <v>0.5985558771112059</v>
       </c>
       <c r="F5" t="n">
-        <v>7.869564338494824</v>
+        <v>1.278804205005409</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
